--- a/data-manipulation-scripts/sheets-cleanup/sheets/COXIM PARALAMA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/COXIM PARALAMA.xlsx
@@ -31,7 +31,7 @@
     <t>7898590342609</t>
   </si>
   <si>
-    <t>COXIM PARALAMA VEDA+ CG TITAN150 192</t>
+    <t>COXIM PARALAMA PEÇA+ CG TITAN150 192</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -92,10 +92,10 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -362,10 +362,12 @@
       <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>20.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>2.5</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
